--- a/data/Перечень работ КР.xlsx
+++ b/data/Перечень работ КР.xlsx
@@ -58,7 +58,7 @@
     <t>Обозначения</t>
   </si>
   <si>
-    <t>Подземная часть здания (до ур. земли)</t>
+    <t>Подземная часть здания (до ур. земли до отм. 0,000)</t>
   </si>
   <si>
     <t>Монолитные ж/б конструкции.</t>
@@ -4727,7 +4727,7 @@
   <dimension ref="A1:O832"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="45.1719" style="1" customWidth="1"/>
+    <col min="1" max="1" width="65.5938" style="1" customWidth="1"/>
     <col min="2" max="2" width="32" style="1" customWidth="1"/>
     <col min="3" max="3" width="44.3516" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.1719" style="1" customWidth="1"/>
